--- a/sales_report_oct.xlsx
+++ b/sales_report_oct.xlsx
@@ -275,7 +275,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'10月販売構成'!$C$4:$C$10</f>
+              <f>'10月販売構成'!$C$4:$C$11</f>
             </numRef>
           </val>
         </ser>
